--- a/bug_report/FeatureOrBugReport_Erdem.xlsx
+++ b/bug_report/FeatureOrBugReport_Erdem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erdmylmz/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erdmylmz/IdeaProjects/REPO/AHAssignment_Erdem/bug_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1D2DC9-1D47-2348-9A8F-80B49A379929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70E2AA92-DA2B-D74D-96A2-53AC66E92644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{61A75899-52F6-124F-815A-876B4089719F}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{61A75899-52F6-124F-815A-876B4089719F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -281,6 +281,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -289,30 +313,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -342,9 +342,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1068659</xdr:colOff>
+      <xdr:colOff>1099634</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>2335566</xdr:rowOff>
+      <xdr:rowOff>2355946</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -374,7 +374,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11534298" y="943667"/>
-          <a:ext cx="3504361" cy="2305679"/>
+          <a:ext cx="3535336" cy="2326059"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -386,15 +386,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>15489</xdr:colOff>
+      <xdr:colOff>46463</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>167424</xdr:rowOff>
+      <xdr:rowOff>46463</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>38720</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1084146</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>2623799</xdr:rowOff>
+      <xdr:rowOff>2849756</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -423,8 +423,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11522928" y="3450839"/>
-          <a:ext cx="3616402" cy="2456375"/>
+          <a:off x="11553902" y="3329878"/>
+          <a:ext cx="3500244" cy="2803293"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -687,9 +687,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -727,7 +727,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -833,7 +833,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -975,7 +975,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1000,78 +1000,78 @@
   <sheetData>
     <row r="3" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:12" ht="23" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="12" t="s">
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="2:12" ht="187" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="13" t="s">
+      <c r="G5" s="8"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="2:12" ht="230" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="13" t="s">
+      <c r="G6" s="8"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L6" s="1"/>
@@ -1080,23 +1080,23 @@
       <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="13" t="s">
+      <c r="G7" s="11"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1104,23 +1104,23 @@
       <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="13" t="s">
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1134,6 +1134,9 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Calibri"&amp;10&amp;K000000 Payconiq Internal Use&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>